--- a/vse-loti/339262351/spec-339262351.xlsx
+++ b/vse-loti/339262351/spec-339262351.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -58,12 +61,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,19 +435,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -497,17 +503,77 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Труба Х 14п х 2п х 12000 — 08Х18Н10Т</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>2076</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" s="3" t="n">
+        <v>2076</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>2491.2</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>4309776</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Труба Х 14п х 2п х 12000 — 08Х18Н10Т</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>324</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" s="3" t="n">
+        <v>324</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>388.8</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>104976</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n">
-        <v>0</v>
+      <c r="H4" s="5" t="n">
+        <v>4414752</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Источник: ਫ®¦¥­¨¥ ü 2 ®¡¥ᯥ祭¨ï ¯® ¤®£®¢®àã.doc</t>
         </is>

--- a/vse-loti/339262351/spec-339262351.xlsx
+++ b/vse-loti/339262351/spec-339262351.xlsx
@@ -521,13 +521,13 @@
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" s="3" t="n">
-        <v>2076</v>
+        <v>2685</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>2491.2</v>
+        <v>3275.7</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>4309776</v>
+        <v>5574060</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
@@ -551,13 +551,13 @@
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" s="3" t="n">
-        <v>324</v>
+        <v>2685</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>388.8</v>
+        <v>3275.7</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>104976</v>
+        <v>869940</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -569,13 +569,33 @@
         </is>
       </c>
       <c r="H4" s="5" t="n">
-        <v>4414752</v>
+        <v>6444000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>НМЦК из обоснования:</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>6444000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>НМЦК с НДС 22%:</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>7861680</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Источник: ਫ®¦¥­¨¥ ü 2 ®¡¥ᯥ祭¨ï ¯® ¤®£®¢®àã.doc</t>
+          <t>Источник: ਫ®¦¥­¨¥ ü1 ¯¥æ¨䨪 æ¨ï.xlsx</t>
         </is>
       </c>
     </row>

--- a/vse-loti/339262351/spec-339262351.xlsx
+++ b/vse-loti/339262351/spec-339262351.xlsx
@@ -61,7 +61,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -69,6 +69,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -519,7 +520,9 @@
           <t>м</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" s="2" t="n">
+        <v>1.229</v>
+      </c>
       <c r="F2" s="3" t="n">
         <v>2685</v>
       </c>
@@ -529,8 +532,12 @@
       <c r="H2" s="3" t="n">
         <v>5574060</v>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" s="3" t="n">
+        <v>4535472.97</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>5533277.03</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -549,7 +556,9 @@
           <t>м</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" s="2" t="n">
+        <v>0.192</v>
+      </c>
       <c r="F3" s="3" t="n">
         <v>2685</v>
       </c>
@@ -559,8 +568,12 @@
       <c r="H3" s="3" t="n">
         <v>869940</v>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" s="3" t="n">
+        <v>4535472.97</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>5533277.03</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -568,7 +581,10 @@
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="E4" s="5" t="n">
+        <v>1.421</v>
+      </c>
+      <c r="H4" s="6" t="n">
         <v>6444000</v>
       </c>
     </row>
@@ -578,7 +594,7 @@
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="6" t="n">
         <v>6444000</v>
       </c>
     </row>
@@ -588,7 +604,7 @@
           <t>НМЦК с НДС 22%:</t>
         </is>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="6" t="n">
         <v>7861680</v>
       </c>
     </row>

--- a/vse-loti/339262351/spec-339262351.xlsx
+++ b/vse-loti/339262351/spec-339262351.xlsx
@@ -66,8 +66,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -447,8 +447,6 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -479,25 +477,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Цена за ед. (без НДС)</t>
+          <t>Стоимость (без НДС)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Цена за ед. (с НДС)</t>
+          <t>Цена за т (без НДС)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Стоимость (без НДС)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
         </is>
@@ -520,24 +508,11 @@
           <t>м</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="3" t="n">
         <v>1.229</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>2685</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>3275.7</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>5574060</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>4535472.97</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>5533277.03</v>
-      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -556,24 +531,11 @@
           <t>м</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.192</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>2685</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>3275.7</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>869940</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>4535472.97</v>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>5533277.03</v>
-      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -584,9 +546,6 @@
       <c r="E4" s="5" t="n">
         <v>1.421</v>
       </c>
-      <c r="H4" s="6" t="n">
-        <v>6444000</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -594,7 +553,7 @@
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="F5" s="6" t="n">
         <v>6444000</v>
       </c>
     </row>
@@ -604,14 +563,14 @@
           <t>НМЦК с НДС 22%:</t>
         </is>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="F6" s="6" t="n">
         <v>7861680</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Источник: ਫ®¦¥­¨¥ ü1 ¯¥æ¨䨪 æ¨ï.xlsx</t>
+          <t>Источник: 1224785 ТЗ_поставка бесшовных труб ТУ 14-3Р-197-2001.pdf</t>
         </is>
       </c>
     </row>
